--- a/Manual/source/tab/connectorsEN.xlsx
+++ b/Manual/source/tab/connectorsEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="52"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="48"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -1218,6 +1218,15 @@
     <t xml:space="preserve">Analog ground</t>
   </si>
   <si>
+    <t xml:space="preserve">PT1000_2+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input for 2. PT1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT1000_2-</t>
+  </si>
+  <si>
     <t xml:space="preserve">PT1000_1+</t>
   </si>
   <si>
@@ -1225,15 +1234,6 @@
   </si>
   <si>
     <t xml:space="preserve">PT1000_1-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT1000_2+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input for 2. PT1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT1000_2-</t>
   </si>
   <si>
     <t xml:space="preserve">DITTL1</t>

--- a/Manual/source/tab/connectorsEN.xlsx
+++ b/Manual/source/tab/connectorsEN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="48"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="438">
   <si>
     <t xml:space="preserve">This is a workbook with source tables of TGZ/TGS connector descriptions in English. Each sheet corresponds to one unique connector type. Since connectors are often repeated within TGZ (typically those on the control board), they are only listed once. I.e. E.g. IO connector 22pin weidmuller B2CF is used over and over again, so it is only listed here once as "X8_IO_22pin_B2CF"</t>
   </si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t xml:space="preserve">13-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+B2</t>
   </si>
   <si>
     <t xml:space="preserve">+ Brake motor 2</t>
@@ -7890,12 +7893,11 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <f aca="false">+B2</f>
-        <v>-B2</v>
+      <c r="B3" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>231</v>
@@ -7909,7 +7911,7 @@
         <v>220</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>231</v>
@@ -7923,7 +7925,7 @@
         <v>221</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>231</v>
@@ -7934,10 +7936,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>231</v>
@@ -7948,10 +7950,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>231</v>
@@ -8007,10 +8009,10 @@
         <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8018,13 +8020,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8038,7 +8040,7 @@
         <v>119</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8052,7 +8054,7 @@
         <v>111</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8066,7 +8068,7 @@
         <v>113</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -8116,10 +8118,10 @@
         <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8127,13 +8129,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8144,10 +8146,10 @@
         <v>221</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8158,10 +8160,10 @@
         <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -8211,10 +8213,10 @@
         <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8225,10 +8227,10 @@
         <v>171</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8239,10 +8241,10 @@
         <v>171</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8253,10 +8255,10 @@
         <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -8303,13 +8305,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8317,13 +8319,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8377,7 @@
         <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8389,7 +8391,7 @@
         <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8403,7 +8405,7 @@
         <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8417,7 +8419,7 @@
         <v>210</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8431,7 +8433,7 @@
         <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8445,7 +8447,7 @@
         <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8500,7 +8502,7 @@
         <v>226</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8508,13 +8510,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>254</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8522,13 +8524,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8536,13 +8538,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8550,13 +8552,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8564,13 +8566,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8578,13 +8580,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8592,13 +8594,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>226</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8606,13 +8608,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8620,13 +8622,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8676,7 +8678,7 @@
         <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -8759,7 +8761,7 @@
         <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8773,7 +8775,7 @@
         <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8787,7 +8789,7 @@
         <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8801,7 +8803,7 @@
         <v>210</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8815,7 +8817,7 @@
         <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8829,7 +8831,7 @@
         <v>214</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8884,7 +8886,7 @@
         <v>226</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8892,13 +8894,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8906,13 +8908,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8920,13 +8922,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8934,13 +8936,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8948,13 +8950,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8962,13 +8964,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8976,13 +8978,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8990,13 +8992,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9004,13 +9006,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9018,13 +9020,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9032,13 +9034,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -9192,13 +9194,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9206,13 +9208,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9488,7 +9490,7 @@
         <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9502,7 +9504,7 @@
         <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9510,13 +9512,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9524,13 +9526,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9585,7 +9587,7 @@
         <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9599,7 +9601,7 @@
         <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9607,13 +9609,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9621,13 +9623,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,10 +9690,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -9702,10 +9704,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
@@ -9754,10 +9756,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -9768,10 +9770,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -9782,7 +9784,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>226</v>
@@ -9796,10 +9798,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -9810,10 +9812,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>10</v>
@@ -9824,10 +9826,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -9838,10 +9840,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>10</v>
@@ -9852,10 +9854,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -9917,13 +9919,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9931,13 +9933,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9945,13 +9947,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9959,13 +9961,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -10012,13 +10014,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10026,13 +10028,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10040,13 +10042,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10054,13 +10056,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -10103,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>164</v>
@@ -10114,7 +10116,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>162</v>
@@ -10125,7 +10127,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>160</v>
@@ -10136,7 +10138,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>158</v>
@@ -10147,7 +10149,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>156</v>
@@ -10158,7 +10160,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>154</v>
@@ -10169,7 +10171,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>152</v>
@@ -10180,7 +10182,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>150</v>
@@ -10191,10 +10193,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10202,10 +10204,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10318,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>164</v>
@@ -10329,7 +10331,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>162</v>
@@ -10340,7 +10342,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>160</v>
@@ -10351,7 +10353,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>158</v>
@@ -10362,7 +10364,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>156</v>
@@ -10373,7 +10375,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>154</v>
@@ -10384,7 +10386,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>152</v>
@@ -10395,7 +10397,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>150</v>
@@ -10406,10 +10408,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10417,10 +10419,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10458,7 +10460,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>174</v>
@@ -10469,24 +10471,24 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10565,13 +10567,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10579,13 +10581,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10596,10 +10598,10 @@
         <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10610,10 +10612,10 @@
         <v>185</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10627,7 +10629,7 @@
         <v>119</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -10915,7 +10917,7 @@
         <v>180</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11048,7 +11050,7 @@
         <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11090,7 +11092,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11099,7 +11101,7 @@
         <v>198</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11107,7 +11109,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11116,7 +11118,7 @@
         <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11124,7 +11126,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>190</v>
@@ -11133,7 +11135,7 @@
         <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11141,7 +11143,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>189</v>
@@ -11150,7 +11152,7 @@
         <v>192</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11201,7 +11203,7 @@
         <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11218,7 +11220,7 @@
         <v>186</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11297,7 +11299,7 @@
         <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11339,7 +11341,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11348,7 +11350,7 @@
         <v>198</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11356,7 +11358,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11365,7 +11367,7 @@
         <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11373,7 +11375,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>190</v>
@@ -11382,7 +11384,7 @@
         <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11390,7 +11392,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>189</v>
@@ -11399,7 +11401,7 @@
         <v>192</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11512,7 +11514,7 @@
         <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11554,7 +11556,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11563,7 +11565,7 @@
         <v>198</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11571,7 +11573,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11580,7 +11582,7 @@
         <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11588,7 +11590,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>190</v>
@@ -11597,7 +11599,7 @@
         <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11605,7 +11607,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>189</v>
@@ -11614,7 +11616,7 @@
         <v>192</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11728,10 +11730,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11742,7 +11744,7 @@
         <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11750,10 +11752,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11761,10 +11763,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11772,10 +11774,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11783,10 +11785,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11794,10 +11796,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11808,7 +11810,7 @@
         <v>147</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11816,10 +11818,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11830,7 +11832,7 @@
         <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11838,10 +11840,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11852,7 +11854,7 @@
         <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12246,7 +12248,7 @@
         <v>163</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12257,7 +12259,7 @@
         <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12268,7 +12270,7 @@
         <v>159</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12279,7 +12281,7 @@
         <v>157</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12290,7 +12292,7 @@
         <v>155</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12301,7 +12303,7 @@
         <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12312,7 +12314,7 @@
         <v>151</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12323,7 +12325,7 @@
         <v>149</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12331,10 +12333,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12342,10 +12344,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12353,10 +12355,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12364,10 +12366,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12378,7 +12380,7 @@
         <v>141</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12389,7 +12391,7 @@
         <v>139</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12400,7 +12402,7 @@
         <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12411,7 +12413,7 @@
         <v>135</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12422,7 +12424,7 @@
         <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12433,7 +12435,7 @@
         <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -12476,10 +12478,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12487,10 +12489,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12498,10 +12500,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12509,10 +12511,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12520,10 +12522,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12531,10 +12533,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12542,10 +12544,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12553,10 +12555,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -12599,10 +12601,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12610,10 +12612,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12621,10 +12623,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12632,10 +12634,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12643,10 +12645,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12657,7 +12659,7 @@
         <v>118</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12665,10 +12667,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12676,10 +12678,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12687,10 +12689,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12698,10 +12700,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12753,10 +12755,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12764,10 +12766,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12775,10 +12777,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12786,10 +12788,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12797,10 +12799,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12808,10 +12810,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12819,10 +12821,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12830,10 +12832,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
